--- a/data/trans_dic/IP12B$oido-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP12B$oido-Estudios-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -523,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han limitado su actividad por síntomas o dolor de oídos, otitis</t>
+          <t>Menores que han limitado su actividad por síntomas o dolor de oídos, otitis (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 20,75</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 33,27</t>
+          <t>0,0; 34,17</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 37,95</t>
+          <t>0,0; 44,53</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 52,59</t>
+          <t>0,0; 52,34</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0; 17,08</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 32,73</t>
+          <t>0,0; 32,7</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,37</t>
+          <t>0,0; 20,3</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 35,03</t>
+          <t>0,0; 27,97</t>
         </is>
       </c>
     </row>
@@ -787,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,7</t>
+          <t>0,0; 13,34</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,11; 18,71</t>
+          <t>2,14; 20,51</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,71; 15,83</t>
+          <t>1,71; 16,79</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,79</t>
+          <t>0,0; 12,16</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,58; 14,27</t>
+          <t>1,53; 14,01</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,55; 15,33</t>
+          <t>1,57; 15,53</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,85; 7,58</t>
+          <t>0,86; 8,44</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,17; 12,98</t>
+          <t>3,2; 13,37</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,58; 11,7</t>
+          <t>2,02; 11,31</t>
         </is>
       </c>
     </row>
@@ -897,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,34</t>
+          <t>0,0; 31,73</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,53</t>
+          <t>0,0; 25,9</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,21</t>
+          <t>0,0; 22,32</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 40,47</t>
+          <t>0,0; 39,49</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 43,78</t>
+          <t>0,0; 43,69</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 13,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,8; 25,36</t>
+          <t>2,88; 28,11</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,68; 25,22</t>
+          <t>2,85; 26,35</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,68</t>
+          <t>0,0; 13,56</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,18; 10,43</t>
+          <t>1,17; 10,68</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,52; 15,36</t>
+          <t>3,48; 15,32</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,07; 12,18</t>
+          <t>2,1; 12,43</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,46; 12,29</t>
+          <t>1,46; 13,16</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,35; 14,11</t>
+          <t>2,62; 14,07</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,2; 11,86</t>
+          <t>1,17; 10,94</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,2; 9,77</t>
+          <t>2,02; 8,96</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,33; 11,9</t>
+          <t>4,02; 12,14</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,52; 10,2</t>
+          <t>2,19; 9,28</t>
         </is>
       </c>
     </row>
@@ -1071,4 +1072,791 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que han limitado su actividad por síntomas o dolor de oídos, otitis (tasa de respuesta: 99,36%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Primarios</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>710</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>564</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>710</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>564</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3438</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2930</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2881</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3648</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3474</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2467</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>1247</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>2871</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>1903</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>672</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>2612</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>1983</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>1919</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>5482</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>3886</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3953</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>750; 7188</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>544; 5341</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3813</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>693; 6348</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>571; 5648</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>525; 5147</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>2571; 10738</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>1379; 7714</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Universitarios</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>520</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>1335</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>715</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>1323</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>1689</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>1843</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>3024</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>715</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2728</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4191</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3734</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3892</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4901</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>531; 5188</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>781; 7220</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3523</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>1767</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>4915</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>3183</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>2696</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>4301</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>1983</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>4462</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>9216</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>5166</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>513; 4685</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>2134; 9388</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>1157; 6853</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>681; 6145</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>1667; 8940</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>561; 5237</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>1827; 8113</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>5025; 15153</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>2257; 9558</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP12B$oido-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP12B$oido-Estudios-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han limitado su actividad por síntomas o dolor de oídos, otitis (tasa de respuesta: 99,36%)</t>
+          <t>Menores que en las últimas 2 semanas han limitado su actividad por síntomas o dolor de oídos, otitis (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -683,7 +683,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 34,17</t>
+          <t>0,0; 32,17</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -693,7 +693,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 52,34</t>
+          <t>0,0; 60,85</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -708,17 +708,17 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 32,7</t>
+          <t>0,0; 26,44</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,3</t>
+          <t>0,0; 21,11</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,97</t>
+          <t>0,0; 33,17</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,34</t>
+          <t>0,0; 15,3</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,14; 20,51</t>
+          <t>2,11; 18,41</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,71; 16,79</t>
+          <t>1,68; 14,81</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,16</t>
+          <t>0,0; 10,78</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,53; 14,01</t>
+          <t>1,57; 13,37</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,57; 15,53</t>
+          <t>1,55; 13,44</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,86; 8,44</t>
+          <t>0,87; 8,51</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,2; 13,37</t>
+          <t>2,8; 12,21</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,02; 11,31</t>
+          <t>2,08; 11,34</t>
         </is>
       </c>
     </row>
@@ -898,27 +898,27 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 31,73</t>
+          <t>0,0; 32,81</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,9</t>
+          <t>0,0; 30,72</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,32</t>
+          <t>0,0; 21,48</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 39,49</t>
+          <t>0,0; 40,05</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 43,69</t>
+          <t>0,0; 40,94</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -928,17 +928,17 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,88; 28,11</t>
+          <t>2,86; 28,24</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,85; 26,35</t>
+          <t>2,61; 24,93</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,56</t>
+          <t>0,0; 13,91</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,17; 10,68</t>
+          <t>1,18; 11,42</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,48; 15,32</t>
+          <t>3,4; 15,52</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,1; 12,43</t>
+          <t>2,05; 12,72</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,46; 13,16</t>
+          <t>1,49; 14,1</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,62; 14,07</t>
+          <t>2,38; 13,98</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,17; 10,94</t>
+          <t>1,16; 10,82</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,02; 8,96</t>
+          <t>1,92; 10,04</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,02; 12,14</t>
+          <t>3,98; 11,71</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,19; 9,28</t>
+          <t>2,51; 9,52</t>
         </is>
       </c>
     </row>
@@ -1099,7 +1099,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han limitado su actividad por síntomas o dolor de oídos, otitis (tasa de respuesta: 99,36%)</t>
+          <t>Menores que en las últimas 2 semanas han limitado su actividad por síntomas o dolor de oídos, otitis (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1311,7 +1311,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 3438</t>
+          <t>0; 3237</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -1321,7 +1321,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 2881</t>
+          <t>0; 3349</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1336,17 +1336,17 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 3648</t>
+          <t>0; 2950</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 3474</t>
+          <t>0; 3612</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 2467</t>
+          <t>0; 2925</t>
         </is>
       </c>
     </row>
@@ -1469,47 +1469,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 3953</t>
+          <t>0; 4532</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>750; 7188</t>
+          <t>739; 6451</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>544; 5341</t>
+          <t>536; 4714</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 3813</t>
+          <t>0; 3381</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>693; 6348</t>
+          <t>709; 6055</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>571; 5648</t>
+          <t>565; 4890</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>525; 5147</t>
+          <t>528; 5189</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2571; 10738</t>
+          <t>2250; 9810</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1379; 7714</t>
+          <t>1416; 7733</t>
         </is>
       </c>
     </row>
@@ -1632,27 +1632,27 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 2728</t>
+          <t>0; 2820</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 4191</t>
+          <t>0; 4971</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 3734</t>
+          <t>0; 3593</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 3892</t>
+          <t>0; 3947</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 4901</t>
+          <t>0; 4593</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1662,17 +1662,17 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>531; 5188</t>
+          <t>529; 5211</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>781; 7220</t>
+          <t>715; 6832</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 3523</t>
+          <t>0; 3612</t>
         </is>
       </c>
     </row>
@@ -1795,47 +1795,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>513; 4685</t>
+          <t>519; 5013</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2134; 9388</t>
+          <t>2083; 9514</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1157; 6853</t>
+          <t>1132; 7010</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>681; 6145</t>
+          <t>697; 6587</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1667; 8940</t>
+          <t>1511; 8885</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>561; 5237</t>
+          <t>556; 5178</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1827; 8113</t>
+          <t>1742; 9092</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>5025; 15153</t>
+          <t>4975; 14624</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2257; 9558</t>
+          <t>2582; 9799</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP12B$oido-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP12B$oido-Estudios-trans_dic.xlsx
@@ -530,14 +530,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -625,32 +625,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>12,73%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>7,05%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>8,57%</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>12,73%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>0,0; 52,59</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 32,17</t>
-        </is>
-      </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 44,53</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 60,85</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 33,27</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 37,95</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,44</t>
+          <t>0,0; 32,73</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,11</t>
+          <t>0,0; 21,37</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 33,17</t>
+          <t>0,0; 35,03</t>
         </is>
       </c>
     </row>
@@ -735,32 +735,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>2,14%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>5,77%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>5,45%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>4,21%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>8,19%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>5,98%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>2,14%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>5,77%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>5,45%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,3</t>
+          <t>0,0; 10,79</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,11; 18,41</t>
+          <t>1,58; 14,27</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,68; 14,81</t>
+          <t>1,55; 15,33</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,78</t>
+          <t>0,0; 13,7</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,57; 13,37</t>
+          <t>2,11; 18,71</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,55; 13,44</t>
+          <t>1,71; 15,83</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,87; 8,51</t>
+          <t>0,85; 7,58</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,8; 12,21</t>
+          <t>3,17; 12,98</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,08; 11,34</t>
+          <t>2,58; 11,7</t>
         </is>
       </c>
     </row>
@@ -845,32 +845,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>13,43%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>15,06%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>6,05%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>8,25%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>4,28%</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>13,43%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>15,06%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 32,81</t>
+          <t>0,0; 40,47</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,72</t>
+          <t>0,0; 43,78</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,48</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 40,05</t>
+          <t>0,0; 28,34</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 40,94</t>
+          <t>0,0; 25,53</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 20,21</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,86; 28,24</t>
+          <t>2,8; 25,36</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,61; 24,93</t>
+          <t>2,68; 25,22</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,91</t>
+          <t>0,0; 13,68</t>
         </is>
       </c>
     </row>
@@ -955,32 +955,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>5,77%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>6,77%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>4,14%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>4,03%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>8,02%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>5,77%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>5,77%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>6,77%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>4,14%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,18; 11,42</t>
+          <t>1,46; 12,29</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,4; 15,52</t>
+          <t>2,35; 14,11</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,05; 12,72</t>
+          <t>1,2; 11,86</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,49; 14,1</t>
+          <t>1,18; 10,43</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,38; 13,98</t>
+          <t>3,52; 15,36</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,16; 10,82</t>
+          <t>2,07; 12,18</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,92; 10,04</t>
+          <t>2,2; 9,77</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3,98; 11,71</t>
+          <t>4,33; 11,9</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,51; 9,52</t>
+          <t>2,52; 10,2</t>
         </is>
       </c>
     </row>
@@ -1105,14 +1105,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -1200,32 +1200,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -1253,32 +1253,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>710</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>564</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>700</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1306,47 +1306,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>0; 2895</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>0; 3237</t>
-        </is>
-      </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 2930</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 3349</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3347</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2497</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 2950</t>
+          <t>0; 3652</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 3612</t>
+          <t>0; 3656</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 2925</t>
+          <t>0; 3090</t>
         </is>
       </c>
     </row>
@@ -1363,22 +1363,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1416,32 +1416,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>672</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>2612</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>1983</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>1247</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>2871</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>1903</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>672</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>2612</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>1983</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1469,47 +1469,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 4532</t>
+          <t>0; 3382</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>739; 6451</t>
+          <t>714; 6462</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>536; 4714</t>
+          <t>562; 5574</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 3381</t>
+          <t>0; 4059</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>709; 6055</t>
+          <t>739; 6556</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>565; 4890</t>
+          <t>544; 5036</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>528; 5189</t>
+          <t>520; 4620</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2250; 9810</t>
+          <t>2544; 10428</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1416; 7733</t>
+          <t>1760; 7981</t>
         </is>
       </c>
     </row>
@@ -1526,32 +1526,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1579,32 +1579,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>1323</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>1689</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
           <t>520</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>1335</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>715</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>1323</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>1689</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1632,47 +1632,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 2820</t>
+          <t>0; 3989</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 4971</t>
+          <t>0; 4911</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 3593</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 3947</t>
+          <t>0; 2436</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 4593</t>
+          <t>0; 4132</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3380</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>529; 5211</t>
+          <t>516; 4680</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>715; 6832</t>
+          <t>735; 6911</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 3612</t>
+          <t>0; 3553</t>
         </is>
       </c>
     </row>
@@ -1689,32 +1689,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1742,32 +1742,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>2696</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>4301</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>1983</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>1767</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>4915</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>3183</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>2696</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>4301</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>1983</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1795,47 +1795,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>519; 5013</t>
+          <t>682; 5742</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2083; 9514</t>
+          <t>1494; 8966</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1132; 7010</t>
+          <t>573; 5674</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>697; 6587</t>
+          <t>517; 4578</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1511; 8885</t>
+          <t>2155; 9416</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>556; 5178</t>
+          <t>1139; 6714</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1742; 9092</t>
+          <t>1988; 8848</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>4975; 14624</t>
+          <t>5406; 14851</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2582; 9799</t>
+          <t>2598; 10505</t>
         </is>
       </c>
     </row>
